--- a/data/trans_orig/P29-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P29-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65008</t>
+          <t>66654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97012</t>
+          <t>97673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109382</t>
+          <t>108378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143267</t>
+          <t>143987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>183768</t>
+          <t>183702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230123</t>
+          <t>230184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>34764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58564</t>
+          <t>59975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47982</t>
+          <t>47310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74706</t>
+          <t>76288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88470</t>
+          <t>89027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125759</t>
+          <t>127029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131557</t>
+          <t>130460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164392</t>
+          <t>164523</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58925</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>89087</t>
+          <t>88802</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>195363</t>
+          <t>196635</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>242653</t>
+          <t>242356</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130153</t>
+          <t>131116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172450</t>
+          <t>175350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279270</t>
+          <t>279887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323965</t>
+          <t>323334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>424266</t>
+          <t>423211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>485533</t>
+          <t>485058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133557</t>
+          <t>130822</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112487</t>
+          <t>111863</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>148488</t>
+          <t>149789</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215686</t>
+          <t>217768</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>269625</t>
+          <t>271469</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>206477</t>
+          <t>205204</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>251062</t>
+          <t>251454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58562</t>
+          <t>59784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91376</t>
+          <t>90436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>273135</t>
+          <t>275765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>329336</t>
+          <t>331710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53783</t>
+          <t>53618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82872</t>
+          <t>81827</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>161246</t>
+          <t>159534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>196155</t>
+          <t>194686</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222433</t>
+          <t>222096</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>271165</t>
+          <t>269935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>45655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73027</t>
+          <t>73197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55847</t>
+          <t>55998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86010</t>
+          <t>85309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108473</t>
+          <t>107655</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149764</t>
+          <t>147402</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176437</t>
+          <t>176062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210853</t>
+          <t>211155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73511</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103177</t>
+          <t>105866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256001</t>
+          <t>256816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305068</t>
+          <t>306047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46515</t>
+          <t>46027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71965</t>
+          <t>72993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118885</t>
+          <t>120056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155265</t>
+          <t>155025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171322</t>
+          <t>174255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217047</t>
+          <t>221050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50479</t>
+          <t>47237</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79129</t>
+          <t>78311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89119</t>
+          <t>87240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122723</t>
+          <t>120018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147326</t>
+          <t>144303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191795</t>
+          <t>188688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>220203</t>
+          <t>219404</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252755</t>
+          <t>254073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113026</t>
+          <t>112617</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>149982</t>
+          <t>148007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>341092</t>
+          <t>340564</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>393573</t>
+          <t>394140</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50191</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76753</t>
+          <t>75196</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>100681</t>
+          <t>101840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131426</t>
+          <t>131396</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158865</t>
+          <t>158993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198710</t>
+          <t>199676</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32238</t>
+          <t>33359</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56205</t>
+          <t>57138</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>33072</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57088</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71522</t>
+          <t>72306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>105631</t>
+          <t>105263</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83122</t>
+          <t>82972</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112752</t>
+          <t>110879</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36123</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61197</t>
+          <t>60009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126358</t>
+          <t>125174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164096</t>
+          <t>164121</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>33020</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>57127</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99592</t>
+          <t>99019</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>134391</t>
+          <t>131958</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>137561</t>
+          <t>137610</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>178889</t>
+          <t>180152</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43928</t>
+          <t>43572</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39300</t>
+          <t>40160</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68431</t>
+          <t>68895</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102184</t>
+          <t>100205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>180307</t>
+          <t>180151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>207699</t>
+          <t>207776</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95831</t>
+          <t>96086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>128855</t>
+          <t>129881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>285424</t>
+          <t>283883</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>328710</t>
+          <t>331378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>201721</t>
+          <t>201601</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>250538</t>
+          <t>251958</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>385752</t>
+          <t>383188</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>434236</t>
+          <t>430702</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>600116</t>
+          <t>596034</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>670560</t>
+          <t>668913</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>79891</t>
+          <t>80674</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116360</t>
+          <t>115704</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>81529</t>
+          <t>80683</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117830</t>
+          <t>115850</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>172811</t>
+          <t>171535</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>224058</t>
+          <t>222093</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>265995</t>
+          <t>265985</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>317325</t>
+          <t>315502</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112596</t>
+          <t>114762</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151299</t>
+          <t>152368</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>390176</t>
+          <t>388539</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>457794</t>
+          <t>457536</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142756</t>
+          <t>142842</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>188759</t>
+          <t>187962</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>374253</t>
+          <t>375124</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>431469</t>
+          <t>430657</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>531294</t>
+          <t>528439</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>609294</t>
+          <t>605887</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>71067</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>106271</t>
+          <t>106484</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>119646</t>
+          <t>120899</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>163087</t>
+          <t>163148</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>201434</t>
+          <t>201264</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>257714</t>
+          <t>257040</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>467263</t>
+          <t>468263</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>518865</t>
+          <t>520095</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>214986</t>
+          <t>216902</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>267633</t>
+          <t>266641</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>694721</t>
+          <t>693441</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>772576</t>
+          <t>769357</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>804658</t>
+          <t>802564</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>906429</t>
+          <t>900023</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1728429</t>
+          <t>1719761</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1839822</t>
+          <t>1847016</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2556065</t>
+          <t>2563608</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2716679</t>
+          <t>2717815</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>500418</t>
+          <t>503282</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>586846</t>
+          <t>587875</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>653414</t>
+          <t>649158</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>748064</t>
+          <t>746706</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1174469</t>
+          <t>1177769</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1302182</t>
+          <t>1307266</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1821344</t>
+          <t>1829096</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1937089</t>
+          <t>1937077</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>844598</t>
+          <t>842806</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>949631</t>
+          <t>949667</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2705088</t>
+          <t>2701121</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2865563</t>
+          <t>2862436</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65741</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96725</t>
+          <t>96229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>129323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164205</t>
+          <t>163810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200822</t>
+          <t>202445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251976</t>
+          <t>251661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52777</t>
+          <t>51936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>44907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55381</t>
+          <t>55459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86955</t>
+          <t>88001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>158000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>192165</t>
+          <t>193097</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93143</t>
+          <t>90639</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127297</t>
+          <t>126851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>260695</t>
+          <t>258662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>313179</t>
+          <t>309893</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,25%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123486</t>
+          <t>125515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167571</t>
+          <t>167020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>268005</t>
+          <t>267339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314363</t>
+          <t>314436</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404477</t>
+          <t>408185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>468071</t>
+          <t>473057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36607</t>
+          <t>37364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63682</t>
+          <t>66411</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63774</t>
+          <t>65261</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98243</t>
+          <t>99197</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110780</t>
+          <t>108744</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>151883</t>
+          <t>153184</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285930</t>
+          <t>285967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>332732</t>
+          <t>331475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130118</t>
+          <t>132310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173370</t>
+          <t>174233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>433646</t>
+          <t>426665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>500080</t>
+          <t>491769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68242</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99670</t>
+          <t>102952</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146697</t>
+          <t>145703</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184342</t>
+          <t>184163</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>226073</t>
+          <t>223758</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274646</t>
+          <t>274325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48563</t>
+          <t>48965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39473</t>
+          <t>38245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64756</t>
+          <t>64256</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>73264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107197</t>
+          <t>106725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184294</t>
+          <t>183779</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219326</t>
+          <t>219829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106140</t>
+          <t>105486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142379</t>
+          <t>144233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302078</t>
+          <t>300279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>352234</t>
+          <t>352918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81601</t>
+          <t>81846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116340</t>
+          <t>120766</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203215</t>
+          <t>204984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>244804</t>
+          <t>243983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>295825</t>
+          <t>297641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>349952</t>
+          <t>354230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66322</t>
+          <t>68503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101963</t>
+          <t>101667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60809</t>
+          <t>62395</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93429</t>
+          <t>94483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138268</t>
+          <t>137225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185848</t>
+          <t>184390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170639</t>
+          <t>169782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211561</t>
+          <t>209600</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72105</t>
+          <t>71473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106003</t>
+          <t>106274</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>252797</t>
+          <t>249788</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>307905</t>
+          <t>305143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>35227</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61349</t>
+          <t>61767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111874</t>
+          <t>111915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140648</t>
+          <t>140968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>150634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198100</t>
+          <t>193565</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>26661</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48565</t>
+          <t>48925</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29320</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49845</t>
+          <t>50521</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>61028</t>
+          <t>62530</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>93373</t>
+          <t>93626</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113559</t>
+          <t>112656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143009</t>
+          <t>143410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66947</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>162005</t>
+          <t>162150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>202077</t>
+          <t>206230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42172</t>
+          <t>41496</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70107</t>
+          <t>69168</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125236</t>
+          <t>125538</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>158812</t>
+          <t>158465</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>174122</t>
+          <t>173477</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>221849</t>
+          <t>219748</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>45875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61141</t>
+          <t>61587</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96514</t>
+          <t>94492</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>169321</t>
+          <t>168841</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>201377</t>
+          <t>200245</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80158</t>
+          <t>79929</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112003</t>
+          <t>111983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>255463</t>
+          <t>257164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>303051</t>
+          <t>304978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132897</t>
+          <t>135361</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178631</t>
+          <t>180265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>343549</t>
+          <t>342749</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>396499</t>
+          <t>394243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>490134</t>
+          <t>487603</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>561414</t>
+          <t>567138</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>89767</t>
+          <t>89621</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>132823</t>
+          <t>129320</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92013</t>
+          <t>91987</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>131236</t>
+          <t>130913</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>190572</t>
+          <t>193630</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>251067</t>
+          <t>250090</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>368757</t>
+          <t>370183</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>424864</t>
+          <t>424361</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>191667</t>
+          <t>190176</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>241287</t>
+          <t>239649</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>573991</t>
+          <t>575788</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>652530</t>
+          <t>649502</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>249773</t>
+          <t>245995</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>305759</t>
+          <t>302781</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>528963</t>
+          <t>528524</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>585262</t>
+          <t>586326</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>790060</t>
+          <t>794616</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>876286</t>
+          <t>879095</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>36357</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>63713</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>32535</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>59590</t>
+          <t>59950</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>75142</t>
+          <t>76391</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>116030</t>
+          <t>116386</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>425410</t>
+          <t>426758</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>485048</t>
+          <t>484269</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>193481</t>
+          <t>193615</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>247046</t>
+          <t>245426</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>632848</t>
+          <t>627222</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>715943</t>
+          <t>714801</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>891280</t>
+          <t>893521</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1000145</t>
+          <t>998833</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1965565</t>
+          <t>1966518</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2087090</t>
+          <t>2088174</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2881319</t>
+          <t>2884297</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3047949</t>
+          <t>3053309</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>398228</t>
+          <t>399242</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>475914</t>
+          <t>480178</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>435303</t>
+          <t>433110</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>517018</t>
+          <t>519327</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>853749</t>
+          <t>857725</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>973490</t>
+          <t>973628</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1987829</t>
+          <t>1985146</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2106482</t>
+          <t>2105949</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>996922</t>
+          <t>1001655</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1112730</t>
+          <t>1109914</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3017216</t>
+          <t>3015447</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3185352</t>
+          <t>3184731</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>41337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68396</t>
+          <t>70036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91332</t>
+          <t>90376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124074</t>
+          <t>123715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141787</t>
+          <t>139807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185641</t>
+          <t>185081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46350</t>
+          <t>47180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77040</t>
+          <t>76554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59022</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89416</t>
+          <t>88790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113951</t>
+          <t>112929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156242</t>
+          <t>155501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160343</t>
+          <t>161449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>196466</t>
+          <t>196213</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90989</t>
+          <t>91455</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123778</t>
+          <t>123795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>260938</t>
+          <t>262701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>309377</t>
+          <t>310632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83731</t>
+          <t>83060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121283</t>
+          <t>123842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248341</t>
+          <t>248308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293985</t>
+          <t>296514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343529</t>
+          <t>340634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401975</t>
+          <t>402290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113630</t>
+          <t>111437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152013</t>
+          <t>152706</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128086</t>
+          <t>127712</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168806</t>
+          <t>172052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>251645</t>
+          <t>253280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>308872</t>
+          <t>312114</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>246275</t>
+          <t>243867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>291441</t>
+          <t>291749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84187</t>
+          <t>84651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122359</t>
+          <t>121424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>341126</t>
+          <t>340692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>401953</t>
+          <t>400840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73092</t>
+          <t>73613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>105755</t>
+          <t>105853</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85164</t>
+          <t>85368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122418</t>
+          <t>124829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81116</t>
+          <t>81758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114883</t>
+          <t>112182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107752</t>
+          <t>107575</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143996</t>
+          <t>143801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>197470</t>
+          <t>200058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243724</t>
+          <t>247415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188392</t>
+          <t>190568</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222003</t>
+          <t>222775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106053</t>
+          <t>104079</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140361</t>
+          <t>139287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304600</t>
+          <t>304500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353358</t>
+          <t>353244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65332</t>
+          <t>65407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101757</t>
+          <t>101358</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137953</t>
+          <t>138794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147005</t>
+          <t>143377</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194184</t>
+          <t>195501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70074</t>
+          <t>69831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104856</t>
+          <t>102598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98901</t>
+          <t>99377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134677</t>
+          <t>135468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175256</t>
+          <t>178888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225733</t>
+          <t>229891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>213199</t>
+          <t>213842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252037</t>
+          <t>251701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>132499</t>
+          <t>132767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171898</t>
+          <t>171760</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>357715</t>
+          <t>357760</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>414189</t>
+          <t>415733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21278</t>
+          <t>21482</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42739</t>
+          <t>41999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37729</t>
+          <t>38321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63743</t>
+          <t>65541</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84902</t>
+          <t>86811</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>112884</t>
+          <t>114163</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136281</t>
+          <t>134676</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>163151</t>
+          <t>162931</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>230294</t>
+          <t>231949</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>272242</t>
+          <t>271886</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79115</t>
+          <t>76894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105619</t>
+          <t>105902</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26861</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49320</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111214</t>
+          <t>109698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147850</t>
+          <t>147005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>30130</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39156</t>
+          <t>39344</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65415</t>
+          <t>65770</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>55259</t>
+          <t>55218</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87891</t>
+          <t>87577</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41274</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68779</t>
+          <t>68766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98988</t>
+          <t>98901</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132266</t>
+          <t>133017</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147858</t>
+          <t>148250</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193984</t>
+          <t>191164</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>172856</t>
+          <t>173757</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>203000</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89620</t>
+          <t>88560</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>121846</t>
+          <t>122125</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>271681</t>
+          <t>272461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>319025</t>
+          <t>318454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66581</t>
+          <t>67297</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>103455</t>
+          <t>104227</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190210</t>
+          <t>188690</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>238253</t>
+          <t>239601</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>267581</t>
+          <t>265156</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>332410</t>
+          <t>328863</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>163892</t>
+          <t>162086</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>211142</t>
+          <t>210300</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>193196</t>
+          <t>191993</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>241288</t>
+          <t>241410</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>370555</t>
+          <t>366010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>440501</t>
+          <t>435519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>358054</t>
+          <t>356835</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>409748</t>
+          <t>410019</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>236373</t>
+          <t>235332</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>289080</t>
+          <t>286990</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>603087</t>
+          <t>607799</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>681245</t>
+          <t>683934</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>71151</t>
+          <t>70873</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>106058</t>
+          <t>106228</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>212035</t>
+          <t>211822</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>266314</t>
+          <t>264501</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>295073</t>
+          <t>294538</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>363343</t>
+          <t>362920</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>211256</t>
+          <t>209774</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>261945</t>
+          <t>262096</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>289300</t>
+          <t>290489</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>349117</t>
+          <t>347376</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>513785</t>
+          <t>517287</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>590294</t>
+          <t>594764</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>427171</t>
+          <t>429107</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>484170</t>
+          <t>482894</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>238436</t>
+          <t>236440</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>292187</t>
+          <t>291400</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>682488</t>
+          <t>681950</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>765439</t>
+          <t>762461</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,58%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>390976</t>
+          <t>388623</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>470578</t>
+          <t>472713</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1059732</t>
+          <t>1070871</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1180103</t>
+          <t>1181127</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1475752</t>
+          <t>1484026</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1616346</t>
+          <t>1623633</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>903587</t>
+          <t>901417</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1007929</t>
+          <t>1006557</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1202870</t>
+          <t>1207095</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1314510</t>
+          <t>1330245</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2130797</t>
+          <t>2134026</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2288064</t>
+          <t>2299979</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1953610</t>
+          <t>1946076</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2064740</t>
+          <t>2064067</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1091427</t>
+          <t>1100340</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1209526</t>
+          <t>1213283</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3085536</t>
+          <t>3070648</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3250429</t>
+          <t>3246187</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>22953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30321</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47129</t>
+          <t>46544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>43095</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65887</t>
+          <t>65165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61464</t>
+          <t>63223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>108320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93880</t>
+          <t>93576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120851</t>
+          <t>121081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165662</t>
+          <t>165255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217719</t>
+          <t>218356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>188563</t>
+          <t>190546</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>235865</t>
+          <t>234062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130113</t>
+          <t>129455</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159684</t>
+          <t>159365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>332313</t>
+          <t>330368</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>384282</t>
+          <t>383931</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60040</t>
+          <t>62321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102229</t>
+          <t>100389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>178223</t>
+          <t>176772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216974</t>
+          <t>216493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>248425</t>
+          <t>244245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>306404</t>
+          <t>303844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102979</t>
+          <t>102675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154545</t>
+          <t>150294</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137373</t>
+          <t>138506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>174890</t>
+          <t>174192</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252236</t>
+          <t>251209</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>315233</t>
+          <t>315175</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>281538</t>
+          <t>283004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>340548</t>
+          <t>339065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143490</t>
+          <t>144269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183059</t>
+          <t>182372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>438266</t>
+          <t>438001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>509803</t>
+          <t>509426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22048</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44956</t>
+          <t>43356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96769</t>
+          <t>97388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>125296</t>
+          <t>125051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125332</t>
+          <t>123001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163756</t>
+          <t>161388</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75426</t>
+          <t>75900</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108990</t>
+          <t>107978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115191</t>
+          <t>112813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144704</t>
+          <t>144792</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198105</t>
+          <t>199857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242638</t>
+          <t>243509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174644</t>
+          <t>174575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210234</t>
+          <t>209532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94007</t>
+          <t>93971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125904</t>
+          <t>124439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>278753</t>
+          <t>279036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>328086</t>
+          <t>324875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,84%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37132</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68830</t>
+          <t>71310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108852</t>
+          <t>109898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230071</t>
+          <t>232491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172595</t>
+          <t>170483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299984</t>
+          <t>291565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>48028</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81682</t>
+          <t>81542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56793</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120237</t>
+          <t>122236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113808</t>
+          <t>113214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188282</t>
+          <t>187299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>175566</t>
+          <t>174989</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217804</t>
+          <t>217547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151005</t>
+          <t>154341</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>304246</t>
+          <t>315509</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>348900</t>
+          <t>351399</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>512245</t>
+          <t>503123</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94466</t>
+          <t>93677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117023</t>
+          <t>116890</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>148966</t>
+          <t>149124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166301</t>
+          <t>166820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250725</t>
+          <t>248584</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>279525</t>
+          <t>277768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47021</t>
+          <t>47192</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30229</t>
+          <t>29444</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>62848</t>
+          <t>62585</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>86984</t>
+          <t>87331</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27154</t>
+          <t>26508</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45459</t>
+          <t>44517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38545</t>
+          <t>38683</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60445</t>
+          <t>60653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39679</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63366</t>
+          <t>62875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86063</t>
+          <t>85712</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>89230</t>
+          <t>89437</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118758</t>
+          <t>119186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53424</t>
+          <t>53034</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78648</t>
+          <t>77148</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68550</t>
+          <t>66363</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90892</t>
+          <t>90413</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128830</t>
+          <t>126374</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161468</t>
+          <t>161237</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159585</t>
+          <t>159980</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187351</t>
+          <t>187122</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>90862</t>
+          <t>91016</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115962</t>
+          <t>116905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>258860</t>
+          <t>259811</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297086</t>
+          <t>300603</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,16%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>106570</t>
+          <t>105984</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>156038</t>
+          <t>155398</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99625</t>
+          <t>77937</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>271703</t>
+          <t>274607</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>197772</t>
+          <t>200659</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>400377</t>
+          <t>397691</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108730</t>
+          <t>108592</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>157722</t>
+          <t>157183</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85594</t>
+          <t>68720</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>231181</t>
+          <t>229660</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>176198</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>359447</t>
+          <t>359432</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>329797</t>
+          <t>329480</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>389042</t>
+          <t>389752</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>349407</t>
+          <t>347729</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>657767</t>
+          <t>698146</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>718413</t>
+          <t>719046</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1078507</t>
+          <t>1090623</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,38%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>24980</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>87708</t>
+          <t>86774</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>103077</t>
+          <t>101862</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>134705</t>
+          <t>135616</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>109156</t>
+          <t>102899</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>216078</t>
+          <t>216045</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>104334</t>
+          <t>104014</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>325175</t>
+          <t>322084</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>330200</t>
+          <t>332733</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>377164</t>
+          <t>381795</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>357669</t>
+          <t>341236</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>703316</t>
+          <t>698766</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>524325</t>
+          <t>526396</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>797529</t>
+          <t>799999</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>217597</t>
+          <t>218166</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>261470</t>
+          <t>263269</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>730066</t>
+          <t>734052</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1174754</t>
+          <t>1200073</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>396396</t>
+          <t>383287</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>565439</t>
+          <t>558848</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>878297</t>
+          <t>890681</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1159343</t>
+          <t>1170070</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1385623</t>
+          <t>1351442</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1711187</t>
+          <t>1693041</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>635049</t>
+          <t>619525</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>914387</t>
+          <t>910305</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>923005</t>
+          <t>901031</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1216084</t>
+          <t>1212287</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1707113</t>
+          <t>1646294</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2091596</t>
+          <t>2089340</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1996465</t>
+          <t>2003440</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2414665</t>
+          <t>2454165</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1295822</t>
+          <t>1293512</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1857073</t>
+          <t>1861306</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3344938</t>
+          <t>3354584</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4003178</t>
+          <t>4110669</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
